--- a/Outputs/Model Fitting/ESL signal profiles/Multi-sample/modelling_results.xlsx
+++ b/Outputs/Model Fitting/ESL signal profiles/Multi-sample/modelling_results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="34">
   <si>
     <t>Component</t>
   </si>
@@ -91,6 +91,30 @@
   </si>
   <si>
     <t>-123.4</t>
+  </si>
+  <si>
+    <t>S0 = 0.9773 (0.9761, 0.9784); D = 0.4156 (0.414, 0.4173) x1e-3 mm^2/s</t>
+  </si>
+  <si>
+    <t>S0 = 0.9997 (0.9994, 0.9999); D = 0.5525 (0.546, 0.5589) x1e-3 mm^2/s; K = 1.521 (1.477, 1.565)</t>
+  </si>
+  <si>
+    <t>S0 = 0.9946 (0.9937, 0.9956); D = 0.5302 (0.5257, 0.5347) x1e-3 mm^2/s; R = 24.47 (23.84, 25.09) µm</t>
+  </si>
+  <si>
+    <t>S0 = 0.9998 (0.9995, 1); f_sphere = 0.3106 (0.2824, 0.3388); D_sphere = 0.4032 (0.3407, 0.4657) x1e-3 mm^2/s; R = 6.484 (5.842, 7.127) µm; D_ball = 0.6222 (0.5915, 0.653) x1e-3 mm^2/s</t>
+  </si>
+  <si>
+    <t>S0 = 0.9827 (0.9822, 0.9832); D = 0.6753 (0.6741, 0.6765) x1e-3 mm^2/s</t>
+  </si>
+  <si>
+    <t>S0 = 0.9998 (0.9997, 0.9999); D = 0.8595 (0.8546, 0.8645) x1e-3 mm^2/s; K = 0.9243 (0.9091, 0.9396)</t>
+  </si>
+  <si>
+    <t>S0 = 0.9941 (0.9937, 0.9944); D = 0.8082 (0.8047, 0.8116) x1e-3 mm^2/s; R = 35.94 (35.3, 36.58) µm</t>
+  </si>
+  <si>
+    <t>S0 = 0.9997 (0.9996, 0.9999); f_sphere = 0.1912 (0.1811, 0.2012); D_sphere = 0.4464 (0.397, 0.4958) x1e-3 mm^2/s; R = 6.494 (5.998, 6.991) µm; D_ball = 0.9205 (0.9058, 0.9352) x1e-3 mm^2/s</t>
   </si>
 </sst>
 </file>
@@ -139,10 +163,10 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="true"/>
-    <col min="2" max="2" width="12.5703125" customWidth="true"/>
-    <col min="3" max="3" width="158.7109375" customWidth="true"/>
-    <col min="4" max="4" width="6.42578125" customWidth="true"/>
+    <col min="1" max="1" width="10.5546875" customWidth="true"/>
+    <col min="2" max="2" width="11.5546875" customWidth="true"/>
+    <col min="3" max="3" width="151.6640625" customWidth="true"/>
+    <col min="4" max="4" width="6.21875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -167,7 +191,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>18</v>
@@ -181,7 +205,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>19</v>
@@ -195,7 +219,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>20</v>
@@ -209,7 +233,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>21</v>
@@ -223,7 +247,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>22</v>
@@ -237,7 +261,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>23</v>
@@ -251,7 +275,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>24</v>
@@ -265,7 +289,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>25</v>
